--- a/data/argentina/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE17"/>
+  <dimension ref="A1:BE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>h2h_26</t>
+          <t>h2h_25</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>h2h_26_segun_loc</t>
+          <t>h2h_25_segun_loc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -525,187 +525,187 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,42 +717,42 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45512.625</v>
+        <v>45519.70833333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n 
+          <t xml:space="preserve">penel a 
   arg </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio diego armando maradona
-  buenos aires </t>
+          <t xml:space="preserve">estadio centenario ciudad de quilmes
+  quilmes </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>ABogdBtb</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>2024</v>
@@ -764,127 +764,89 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>liga profesional</t>
+          <t>copa argentina</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IH9zbCEt</t>
+          <t>xtEjMiPE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>YXLYMqz6</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+          <t>W8lomLn5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-2.416666666666667</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.9166666666666643</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.9166666666666643</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.08333333333333337</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.5833333333333334</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG2" t="n">
         <v>-1</v>
       </c>
-      <c r="P2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>11.33333333333334</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-8.666666666666666</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>33.66666666666667</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-33.66666666666666</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>70.125</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>70.17561728395061</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
+        <v>69.83084967320261</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-0.875</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.300925925925952</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.1111111111111</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>-1.68001949317739</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.806530214424953</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1057638.888888889</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>862887.9142300196</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.1378167641325536</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.189814814814824</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.121734892787543</v>
-      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>-2.597660818713393</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -892,15 +854,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ngdGLTFj</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45510.88194444445</v>
+        <v>45518.79166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrera d 
+          <t xml:space="preserve">tello f 
   arg </t>
         </is>
       </c>
@@ -912,12 +874,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>QuxS0ahA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UsCR8gFd</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -944,155 +906,155 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>xvR2CVDc</t>
+          <t>IH9zbCEt</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>joU5U5WF</t>
+          <t>r9zDZa4I</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.333333333333332</v>
+        <v>1.4</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.33333333333333</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="X3" t="n">
-        <v>-6.333333333333334</v>
+        <v>13.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.333333333333334</v>
+        <v>-13.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.33333333333334</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="AA3" t="n">
-        <v>-10.33333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.333333333333333</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6666666666666666</v>
+        <v>-4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.4499999999999993</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>69.15555555555557</v>
+        <v>71.06259820426487</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.77727272727273</v>
+        <v>70.125</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+        <v>0.36496953114343</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.354846818304551</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1250659.722222222</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.6095085470085451</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-0.62222222222222</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.9407407407407504</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>0.5851851851851819</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>2.073819966583127</v>
-      </c>
+        <v>-0.305381175354654</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-3.844391025641027</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-1.925480367585635</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>907407.4074074076</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>-1104701.858813701</v>
-      </c>
+        <v>-2.152807657538876</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.488888888888894</v>
-      </c>
+        <v>262144.5489519986</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>0.2911758563074329</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-0.6613304093566796</v>
-      </c>
+        <v>3.905235042735043</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1.828311965811992</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45509.83333333334</v>
+        <v>45516.79166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">penel a 
+          <t xml:space="preserve">gariano a 
   arg </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ciudad de vicente lopez
+          <t xml:space="preserve">estadio jose dellagiovanna
   buenos aires </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
+          <t>nkwO1uw4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIb40wNM</t>
+          <t>tUAxIm6l</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1119,122 +1081,120 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>6ueHTT9o</t>
+          <t>p4iHBcGk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>W8lomLn5</t>
+          <t>IH9zbCEt</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.333333333333332</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="X4" t="n">
-        <v>-0.6666666666666679</v>
+        <v>5.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2</v>
+        <v>-5.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>-10.33333333333334</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>69.40000000000001</v>
-      </c>
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>70.625</v>
+        <v>69.22222222222223</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>-2.847651321398118</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-3.359661258242667</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-1652152.777777778</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-5.602777777777774</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0.5167929292929294</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.867297979797968</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>1.008459595959593</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="n">
-        <v>-0.1549831649831717</v>
-      </c>
+        <v>-2.453959021471661</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-2.266666666666666</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>0.2127597402597416</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>106114.2676767677</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>369418.1096681096</v>
-      </c>
+        <v>0.7889235102889316</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.634217171717168</v>
-      </c>
+        <v>-1069884.267871688</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>0.5691895141895174</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>2.242502405002426</v>
-      </c>
+        <v>-3.390277777777769</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.3458333333333883</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1242,11 +1202,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45509.70833333334</v>
+        <v>45515.83333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1256,18 +1216,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio juan carmelo zerillo
+          <t xml:space="preserve">estadio jorge luis hirschi
   la plata </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jiDN9Zaj</t>
+          <t>p2SkCHXs</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4QmJ2LNc</t>
+          <t>UVatI5Y2</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1294,22 +1254,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IFbJwyX4</t>
+          <t>hhp5qLl8</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8rrQkbdH</t>
+          <t>xvR2CVDc</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1318,97 +1278,111 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>-1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1</v>
+      </c>
       <c r="X5" t="n">
-        <v>6.333333333333334</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.333333333333334</v>
+        <v>-2.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.333333333333336</v>
+        <v>1.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.333333333333336</v>
+        <v>-0.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.75</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.5</v>
+        <v>-2.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>70.94444444444444</v>
+        <v>67.80555555555556</v>
       </c>
       <c r="AK5" t="n">
-        <v>68.4074074074074</v>
+        <v>68.67777777777776</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+        <v>-0.4102598971623053</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-2.233329059184854</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>799386.6873866878</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.7696192696192696</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>0.388047138047142</v>
+        <v>0.1165668828515574</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.4116161616161662</v>
+        <v>-5</v>
       </c>
       <c r="AS5" t="n">
-        <v>-2.437289562289578</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>0.9869310291649356</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.4397953897953819</v>
+      </c>
       <c r="AU5" t="n">
-        <v>-0.1268773165832009</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.762025719378656</v>
+        <v>2.122093629259677</v>
       </c>
       <c r="AW5" t="n">
-        <v>-990761.7845117843</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.01292540792540797</v>
+      </c>
       <c r="AY5" t="n">
-        <v>-1572317.096030331</v>
+        <v>-300000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-614121.0622284792</v>
       </c>
       <c r="BA5" t="n">
-        <v>-2.741582491582506</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>-2.790631100925211</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
+        <v>0.2292009842009861</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-3.564447034447028</v>
+      </c>
       <c r="BD5" t="n">
-        <v>1.626778287072426</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1417,32 +1391,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45509.60416666666</v>
+        <v>45515.72916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">rey hilfer l 
+          <t xml:space="preserve">dovalo p 
   arg </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio guillermo laza
+          <t xml:space="preserve">estadio florencio sola
   buenos aires </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2iZ4q0z6</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0dHZReql</t>
+          <t>UsCR8gFd</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1469,7 +1443,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>nozaSkhA</t>
+          <t>MkIVfIHA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1477,89 +1451,127 @@
           <t>joU5U5WF</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-6.666666666666666</v>
+        <v>-1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
       <c r="X6" t="n">
-        <v>-0.3333333333333321</v>
+        <v>0.04999999999999716</v>
       </c>
       <c r="Y6" t="n">
-        <v>-8.666666666666666</v>
+        <v>-0.04999999999999716</v>
       </c>
       <c r="Z6" t="n">
-        <v>-32.99999999999999</v>
+        <v>-1.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>33.00000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5833333333333333</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.1999999999999993</v>
       </c>
       <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>68.77727272727273</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>69.81874999999999</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-2.966069321671682</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-2.665967729077821</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-944254.4563279855</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-2.634046345811043</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.325655280948041</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.7728758169934657</v>
+      </c>
       <c r="AU6" t="n">
-        <v>6.865079365079367</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>-6.150793650793645</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+        <v>-0.4741518063271783</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
       <c r="AY6" t="n">
-        <v>-759255.9523809524</v>
+        <v>-25000</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
+        <v>-1050997.444324024</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-3</v>
+      </c>
       <c r="BB6" t="n">
-        <v>1.11626984126984</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
+        <v>-2.045335710041599</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.026158645276297</v>
+      </c>
       <c r="BD6" t="n">
-        <v>1.078968253968242</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1568,32 +1580,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n 
+          <t xml:space="preserve">balino j 
   arg </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio monumental jose fierro
-  tucuman </t>
+          <t xml:space="preserve">estadio presidente peron
+  cordoba </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KpqpxWko</t>
+          <t>8G45bXRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eg51aDC4</t>
+          <t>80MMdBdN</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1620,121 +1632,133 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>tdzQkXt9</t>
+          <t>IPCvd5Pa</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>zTfUpJig</t>
+          <t>W8lomLn5</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.333333333333332</v>
+        <v>-1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>8.666666666666666</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="X7" t="n">
-        <v>5.333333333333334</v>
+        <v>-1.5</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>69.27499999999999</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2579160485944669</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1.901434798817704</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>680159.8112535612</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.006594794094781</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-269</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-280</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-1.884792868274559</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.3763694638694624</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.545293591085077</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-2.800000000000011</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-4800000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-213401.5142407087</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.225597319347315</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-3.710282310282309</v>
+      </c>
+      <c r="BD7" t="n">
         <v>-4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8.333333333333336</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-8.333333333333336</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>66.88888888888889</v>
-      </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.170033670033671</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-2.599999999999994</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>192508.4175084175</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>0.471717171717188</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.25555555555556</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1743,32 +1767,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dovalo p 
+          <t xml:space="preserve">espinoza f 
   arg </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ciudad de lanus – nestor diaz perez
-  lanus </t>
+          <t xml:space="preserve">estadio unico madre de ciudades
+  santiago del estero </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Y9yh1J7G</t>
+          <t>0dHZReql</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nkwO1uw4</t>
+          <t>Gdfv0Zsh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1795,129 +1819,131 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>IH9zbCEt</t>
+          <t>YgyxEvnR</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>YgyxEvnR</t>
+          <t>6ueHTT9o</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AE8" t="n">
         <v>5</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-2.333333333333334</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.666666666666668</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.6666666666666661</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-14.66666666666666</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>14.66666666666667</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="AF8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>-0.3448473428611578</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.2066668716692561</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-304488.9169472505</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-2.123877665544327</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-81</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-82</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-3.000826824864674</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.8811447811447763</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.5559263543474096</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-6050000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-135247.834849189</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0.5303872053871999</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-2.281509539842887</v>
+      </c>
+      <c r="BD8" t="n">
         <v>-1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>69.4537037037037</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>69.22222222222223</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.12962962962963</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-0.1342592592592666</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.780092592592595</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-67</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.983459024635494</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.7307440925088</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1448148.148148148</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="n">
-        <v>979903.3748114633</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.136574074074076</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.572046254399211</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-67</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.6717194570135518</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -1926,11 +1952,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508.72916666666</v>
+        <v>45514.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1940,18 +1966,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio alberto j  armando
+          <t xml:space="preserve">estadio monumental
   buenos aires </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hMrWAFH0</t>
+          <t>EVqSBe2f</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hW08cP6J</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1978,135 +2004,129 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>KfMnPVA4</t>
+          <t>xIZruiA3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>fVnsh4kN</t>
+          <t>r9zDZa4I</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="X9" t="n">
-        <v>2.666666666666666</v>
+        <v>19.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2</v>
+        <v>-19.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.333333333333336</v>
+        <v>0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.333333333333336</v>
+        <v>0.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.416666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.08333333333333337</v>
+        <v>-3.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5</v>
+        <v>-1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5</v>
+        <v>-1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.083333333333333</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-2.666666666666667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>66.94444444444444</v>
+        <v>69.8125</v>
       </c>
       <c r="AK9" t="n">
-        <v>69.62291666666667</v>
+        <v>68.5925925925926</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.875</v>
+        <v>4.463078159344107</v>
       </c>
       <c r="AM9" t="n">
-        <v>1500000</v>
+        <v>4.35573347238487</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>3678650.673400673</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>4.809803159803138</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.763888888888889</v>
+        <v>0.1559175607001697</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.875</v>
+        <v>148</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.902777777777771</v>
+        <v>0.4016307979250655</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.397252576920092</v>
-      </c>
+        <v>0.3084162134162121</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>4.312145016109213</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2465972.222222222</v>
-      </c>
+        <v>-0.3362560263129772</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>0.05526936026936036</v>
       </c>
       <c r="AY9" t="n">
-        <v>1362776.582965202</v>
+        <v>8600000</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.169467787114846</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.680555555555557</v>
-      </c>
+        <v>3412713.541139732</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>4.700227521838784</v>
+        <v>5.086724941724952</v>
       </c>
       <c r="BC9" t="n">
-        <v>9</v>
+        <v>-1.663471898471926</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.237455851905992</v>
+        <v>2</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2115,32 +2135,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.78125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez n 
+          <t xml:space="preserve">tello f 
   arg </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio eva peron
-  junin </t>
+          <t xml:space="preserve">estadio juan bautista gargantini
+  mendoza </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>Eg51aDC4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amzaty2s</t>
+          <t>hMrWAFH0</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2167,129 +2187,113 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2Z11gzUL</t>
+          <t>fVnsh4kN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>INpzsZkg</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
+          <t>tdzQkXt9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.333333333333333</v>
+        <v>-0.75</v>
       </c>
       <c r="U10" t="n">
-        <v>6.333333333333332</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>-1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.25</v>
+      </c>
       <c r="X10" t="n">
-        <v>2.666666666666666</v>
+        <v>-14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>-26</v>
+        <v>-0.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>26</v>
+        <v>-0.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3333333333333335</v>
+        <v>-7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-3.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
         <v>-0.3333333333333335</v>
       </c>
-      <c r="AI10" t="n">
-        <v>1.666666666666667</v>
-      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="n">
-        <v>71.48333333333333</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>70.125</v>
-      </c>
+        <v>66.72962962962963</v>
+      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>-4.400966175780425</v>
       </c>
       <c r="AM10" t="n">
-        <v>975000</v>
+        <v>-5.578197867377426</v>
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.592592592592592</v>
+        <v>-0.1440273300830579</v>
       </c>
       <c r="AR10" t="n">
-        <v>-3.504629629629648</v>
+        <v>-6</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1.560185185185176</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>67</v>
-      </c>
+        <v>-1.229877401236536</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="n">
-        <v>-2.308532695374797</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.9339712918660297</v>
+        <v>0.2165042424608963</v>
       </c>
       <c r="AW10" t="n">
-        <v>-128819.4444444447</v>
+        <v>-15</v>
       </c>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="n">
-        <v>-346212.8300549353</v>
+        <v>-1525000</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.03642566010987047</v>
+        <v>-2325043.212022469</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-1.953889774942425</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>0.9729133439659563</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2298,32 +2302,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">echavarria p 
+          <t xml:space="preserve">ramirez n 
   arg </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio 15 de abril
-  santa fe </t>
+          <t xml:space="preserve">estadio gigante de arroyito
+  rosario </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>lr2YMkTK</t>
+          <t>4QmJ2LNc</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EVqSBe2f</t>
+          <t>6gMiRHVj</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2350,60 +2354,64 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>xIZruiA3</t>
+          <t>xYveDhra</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>YXLYMqz6</t>
+          <t>IFbJwyX4</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.333333333333332</v>
+        <v>-0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="X11" t="n">
-        <v>3.333333333333332</v>
+        <v>5.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.666666666666668</v>
+        <v>-5.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>-29.66666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>29.66666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-7.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.5</v>
+        <v>2.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2411,102 +2419,104 @@
       <c r="AG11" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="n">
-        <v>-3.666666666666667</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.3333333333333335</v>
-      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="n">
-        <v>71.33333333333333</v>
+        <v>68.61111111111111</v>
       </c>
       <c r="AK11" t="n">
-        <v>68.38888888888889</v>
+        <v>68.58333333333333</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.07499999999999996</v>
+        <v>2.879401861204087</v>
       </c>
       <c r="AM11" t="n">
-        <v>-5500000</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
+        <v>1.708867146388599</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>559771.6750841753</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.074137205387217</v>
+      </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>222</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.2861111111111114</v>
+        <v>-0.03675352425352441</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.776851851851831</v>
+        <v>218</v>
       </c>
       <c r="AS11" t="n">
-        <v>-3.70185185185187</v>
+        <v>1.44728803552033</v>
       </c>
       <c r="AT11" t="n">
-        <v>-75</v>
+        <v>-0.1408670033670028</v>
       </c>
       <c r="AU11" t="n">
-        <v>-3.026515151515149</v>
+        <v>0.25</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.630050505050505</v>
+        <v>0.7162231998770388</v>
       </c>
       <c r="AW11" t="n">
-        <v>-3660379.62962963</v>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+        <v>7.75</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.05639730639730645</v>
+      </c>
       <c r="AY11" t="n">
-        <v>-3208674.242424243</v>
+        <v>6825000</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.2196969696969697</v>
+        <v>903490.7714272442</v>
       </c>
       <c r="BA11" t="n">
-        <v>-3.706481481481489</v>
+        <v>9.75</v>
       </c>
       <c r="BB11" t="n">
-        <v>-5.767676767676747</v>
+        <v>1.469318181818196</v>
       </c>
       <c r="BC11" t="n">
-        <v>-75</v>
+        <v>0.6278198653198785</v>
       </c>
       <c r="BD11" t="n">
-        <v>-3.23484848484847</v>
+        <v>3</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45507.85416666666</v>
+        <v>45514.60416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">tello f 
+          <t xml:space="preserve">rey hilfer l 
   arg </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio tomas adolfo duco
+          <t xml:space="preserve">estadio pedro bidegain
   buenos aires </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>xd3lGq3F</t>
+          <t>ju1xJoJd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OhapHPm9</t>
+          <t>KpqpxWko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2533,115 +2543,135 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8rrQkbdH</t>
+          <t>xvR2CVDc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>xIZruiA3</t>
+          <t>SdHeJ5BT</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.333333333333332</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.95</v>
+      </c>
       <c r="X12" t="n">
-        <v>0.6666666666666661</v>
+        <v>4.799999999999997</v>
       </c>
       <c r="Y12" t="n">
+        <v>-4.799999999999997</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.6500000000000004</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>5.949999999999999</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>69.37111111111111</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.179340112697361</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.604808269299582</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>979054.1680541679</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.541305916305916</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>146</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>161</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-3.205225291001511</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.192840492840492</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.774331252732448</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.666666666666657</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8175000</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>508503.2763399915</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.120390720390716</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.6466158841158745</v>
+      </c>
+      <c r="BD12" t="n">
         <v>2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-6.333333333333336</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6.333333333333336</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>69.8125</v>
-      </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="n">
-        <v>-2900000</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="n">
-        <v>-74</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.4834835383428704</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-2.474744245524306</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="n">
-        <v>-665358.1070109203</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.01587301587301582</v>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
-        <v>-2.844701213818865</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-74</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0.9376334591807733</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2650,32 +2680,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45507.80208333334</v>
+        <v>45513.875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastrangelo h 
+          <t xml:space="preserve">arasa n 
   arg </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio libertadores de america
+          <t xml:space="preserve">estadio juan domingo peron
   avellaneda </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UVatI5Y2</t>
+          <t>OhapHPm9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>jiDN9Zaj</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2702,22 +2732,22 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SdHeJ5BT</t>
+          <t>8WPFLu92</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>hhp5qLl8</t>
+          <t>UL3R30aD</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2726,111 +2756,109 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6666666666666679</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+        <v>-2.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2</v>
+      </c>
       <c r="X13" t="n">
-        <v>2.666666666666668</v>
+        <v>0.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>-3.333333333333334</v>
+        <v>-0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.333333333333329</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.333333333333329</v>
+        <v>-1.25</v>
       </c>
       <c r="AB13" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="n">
-        <v>66.95833333333334</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>68.85185185185186</v>
-      </c>
+        <v>70.92592592592592</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.03333333333333344</v>
+        <v>4.654902490999277</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5600000</v>
+        <v>4.094231493362898</v>
       </c>
       <c r="AN13" t="n">
-        <v>-4.666666666666668</v>
+        <v>1618809.610528361</v>
       </c>
       <c r="AO13" t="n">
-        <v>-13.66666666666666</v>
+        <v>4.630400155400153</v>
       </c>
       <c r="AP13" t="n">
-        <v>-2</v>
+        <v>-250</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.188888888888886</v>
+        <v>0.03698704676965558</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.24444444444444</v>
+        <v>-293</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.06666666666666288</v>
+        <v>-0.1628233324809969</v>
       </c>
       <c r="AT13" t="n">
-        <v>-152</v>
+        <v>1.364831002331002</v>
       </c>
       <c r="AU13" t="n">
-        <v>-1.849537037037035</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.047619047619051</v>
+        <v>0.3001230707998346</v>
       </c>
       <c r="AW13" t="n">
-        <v>-828611.1111111112</v>
+        <v>-0.1999999999999886</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>0.09375</v>
       </c>
       <c r="AY13" t="n">
-        <v>389897.4867724869</v>
+        <v>-4300000</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.06349206349206349</v>
+        <v>1546900.969983303</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.3333333333333286</v>
+        <v>8.600000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.2113095238095184</v>
+        <v>2.262587412587422</v>
       </c>
       <c r="BC13" t="n">
-        <v>-138</v>
+        <v>1.176772533022529</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.969907407407391</v>
+        <v>-4</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2839,11 +2867,11 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45507.71875</v>
+        <v>45513.79166666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2853,18 +2881,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mario alberto kempes
+          <t xml:space="preserve">estadio julio cesar villagra
   cordoba </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bkDdeAvA</t>
+          <t>Amzaty2s</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8G45bXRA</t>
+          <t>lr2YMkTK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2891,129 +2919,129 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>W8lomLn5</t>
+          <t>YXLYMqz6</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>KfMnPVA4</t>
+          <t>KAydqpwC</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-3</v>
+        <v>14</v>
       </c>
       <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.333333333333334</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="X14" t="n">
-        <v>-1.666666666666666</v>
+        <v>17.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.666666666666668</v>
+        <v>-17.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>0.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>-8</v>
+        <v>0.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.3333333333333334</v>
+        <v>3.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.333333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="n">
-        <v>67.90972222222223</v>
+        <v>72.31666666666666</v>
       </c>
       <c r="AK14" t="n">
-        <v>68.91249999999999</v>
+        <v>70.125</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>0.4774109948022982</v>
       </c>
       <c r="AM14" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
+        <v>-2.323747211661967</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-60493.88111888105</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1.555808080808077</v>
+      </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>146</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.227104377104379</v>
+        <v>0.1036050048349819</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.11346801346798</v>
+        <v>149</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.953367003367006</v>
+        <v>1.574660363790827</v>
       </c>
       <c r="AT14" t="n">
-        <v>-67</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-0.5393696659950535</v>
-      </c>
+        <v>-0.8349067599067546</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="n">
-        <v>3.80174291938998</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>613482.7441077442</v>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+        <v>3.475036573520558</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>0.02670940170940161</v>
+      </c>
       <c r="AY14" t="n">
-        <v>1024993.652431733</v>
+        <v>7100000</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.022138047138043</v>
-      </c>
+        <v>-154546.2175521536</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>2.697944206922543</v>
+        <v>-0.5934731934732014</v>
       </c>
       <c r="BC14" t="n">
-        <v>-67</v>
+        <v>0.09131701631696387</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.846375743279765</v>
+        <v>2</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3022,32 +3050,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.6875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina n 
+          <t xml:space="preserve">trucco s 
   arg </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose amalfitani
-  buenos aires </t>
+          <t xml:space="preserve">claudio fabian tapia
+  barracas </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UsCR8gFd</t>
+          <t>hW08cP6J</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gdfv0Zsh</t>
+          <t>bkDdeAvA</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3074,16 +3102,16 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Czp8uYzj</t>
+          <t>KfMnPVA4</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MkIVfIHA</t>
+          <t>GW9jvbG8</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -3091,102 +3119,112 @@
       <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-8.333333333333334</v>
+        <v>-2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>6.666666666666666</v>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>-11.66666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.66666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>-1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>-2</v>
+        <v>9.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.3333333333333339</v>
-      </c>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="n">
-        <v>68.77727272727273</v>
-      </c>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
+        <v>67.98148148148148</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>69.27499999999999</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-3.413877304998579</v>
+      </c>
       <c r="AM15" t="n">
-        <v>-3050000</v>
+        <v>-3.731464078763835</v>
       </c>
       <c r="AN15" t="n">
-        <v>-2</v>
+        <v>-1318802.031302031</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.400000000000006</v>
+        <v>-3.678860028860029</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>72</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-2.795438820015448</v>
+      </c>
       <c r="AT15" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.7428571428571402</v>
-      </c>
+        <v>-1.188722388722386</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="n">
-        <v>1.990225563909775</v>
+        <v>0.09533002720645811</v>
       </c>
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1202067.669172932</v>
+        <v>1000000</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-1290196.893813026</v>
       </c>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="n">
-        <v>2.055889724310774</v>
+        <v>-2.793967143967137</v>
       </c>
       <c r="BC15" t="n">
-        <v>-78</v>
+        <v>-1.377050727050658</v>
       </c>
       <c r="BD15" t="n">
-        <v>-4.524812030075196</v>
+        <v>1</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -3195,32 +3233,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano a 
+          <t xml:space="preserve">mastrangelo h 
   arg </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio malvinas argentinas
-  mendoza </t>
+          <t xml:space="preserve">estadio guillermo laza
+  buenos aires </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tUAxIm6l</t>
+          <t>2iZ4q0z6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3247,312 +3285,109 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2RU5F8AC</t>
+          <t>YgyxEvnR</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>p4iHBcGk</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
+          <t>nozaSkhA</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="U16" t="n">
         <v>-3</v>
       </c>
-      <c r="P16" t="n">
+      <c r="V16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA16" t="n">
         <v>-1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-7.000000000000002</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.666666666666668</v>
-      </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AD16" t="n">
         <v>-2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>-20.00000000000001</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
         <v>0.3333333333333335</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="n">
-        <v>70.125</v>
-      </c>
-      <c r="AL16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>68.50694444444444</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>-3.522194075697897</v>
+      </c>
       <c r="AM16" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-5.333333333333332</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>8</v>
-      </c>
+        <v>-6.209837007266685</v>
+      </c>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="n">
-        <v>152</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>-1.22895807895808</v>
-      </c>
+        <v>-414</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-444</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.5902570400140519</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="n">
-        <v>1.68074888074888</v>
+        <v>3.020538133127651</v>
       </c>
       <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="n">
-        <v>630761.0907610904</v>
+        <v>-13275000</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-1686886.146970866</v>
       </c>
       <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="n">
-        <v>0.5912291412291353</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>138</v>
-      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="n">
-        <v>3.188156288156222</v>
+        <v>-6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>noM4eJv9</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45506.83333333334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">espinoza f 
-  arg </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio marcelo bielsa
-  rosario </t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>6gMiRHVj</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>p2SkCHXs</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>61</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>liga profesional</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>xvR2CVDc</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>xYveDhra</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-1.333333333333332</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>4.999999999999998</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-5.666666666666671</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5.666666666666671</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-0.4166666666666667</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>68.61111111111111</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>68.67777777777776</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>-0.04074074074074074</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-1325000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-0.6888888888888864</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.362962962962996</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>-0.6481481481481524</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>-3.823611111111113</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>-0.7189814814814781</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>-410925.9259259258</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>115358.7962962964</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-0.1523148148148148</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>-0.1851851851852047</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-3.071759259259267</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>-10</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>-3.824074074074019</v>
-      </c>
-      <c r="BE17" t="n">
         <v>0</v>
       </c>
     </row>
